--- a/stories/arbres/ATOM-REL.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cécile est au jardin avec maman. Elle tient un petit arrosoir bleu. L'eau est tiède. Lila arrive. Lila aimerait l'arrosoir. Cécile peut prêter. Cécile dit : tu peux. C'est ton tour. Elle tend l'arrosoir. Lila arrose le basilic. Ça sent le vert. Cécile attend son tour. Elle s'assoit près de maman. Maman dit : on peut prêter. On peut attendre son tour. On peut aussi proposer un autre jeu. Cécile prend un seau. Elle dit : un autre jeu, le seau. Lila finit. Elle rend l'arrosoir. Cécile arrose la menthe. Parce qu'elle a su prêter, le jeu continue. Maman sourit. Cécile dit : c'est ton tour, puis le mien.</t>
+          <t>Cécile est au jardin avec maman. Elle tient un petit arrosoir bleu. L'eau est tiède. Lila arrive. Lila aimerait l'arrosoir. Cécile peut prêter. Tu peux. C'est ton tour. Elle tend l'arrosoir. Lila arrose le basilic. Ça sent le vert. Cécile attend son tour. Elle s'assoit près de maman. On peut prêter. On peut attendre son tour. On peut aussi proposer un autre jeu. Cécile prend un seau. Un autre jeu, le seau. Lila finit. Elle rend l'arrosoir. Cécile arrose la menthe. Parce qu'elle a su prêter, le jeu continue. Maman sourit. C'est ton tour, puis le mien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile est au jardin avec maman. Elle tient un petit arrosoir bleu. L'eau est tiède. Lila arrive. Lila aimerait l'arrosoir. Cécile peut prêter.
+enfant-f|Tu peux. C'est ton tour. Elle tend l'arrosoir.
+narrateur|Lila arrose le basilic. Ça sent le vert. Cécile attend son tour. Elle s'assoit près de maman.
+maman|On peut prêter. On peut attendre son tour. On peut aussi proposer un autre jeu.
+narrateur|Cécile prend un seau.
+narrateur|Un autre jeu, le seau.
+narrateur|Lila finit. Elle rend l'arrosoir. Cécile arrose la menthe. Parce qu'elle a su prêter, le jeu continue. Maman sourit.
+enfant-f|C'est ton tour, puis le mien.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila veut l'arrosoir. Que peut faire Cécile ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile et Lila rangent l'arrosoir. Maman ferme le robinet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 enfant-f|C'est ton tour, puis le mien.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Lila veut l'arrosoir. Que peut faire Cécile ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Cécile a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Cécile et Lila rangent l'arrosoir. Maman ferme le robinet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cécile prête l'arrosoir</t>
+          <t>L'arrosoir bleu de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le robinet du jardin goutte. Nina tient l'arrosoir bleu. Chouchou le voudrait. Elle prête, attend son tour, puis propose le seau.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cécile est au jardin avec maman. Elle tient un petit arrosoir bleu. L'eau est tiède. Lila arrive. Lila aimerait l'arrosoir. Cécile peut prêter. Tu peux. C'est ton tour. Elle tend l'arrosoir. Lila arrose le basilic. Ça sent le vert. Cécile attend son tour. Elle s'assoit près de maman. On peut prêter. On peut attendre son tour. On peut aussi proposer un autre jeu. Cécile prend un seau. Un autre jeu, le seau. Lila finit. Elle rend l'arrosoir. Cécile arrose la menthe. Parce qu'elle a su prêter, le jeu continue. Maman sourit. C'est ton tour, puis le mien.</t>
+          <t>Le robinet du jardin goutte. Tic. Tic. La terre des pots est encore sombre. Ça sent la menthe. Maman a un tablier mouillé. Un escargot avance sur une feuille. Tu as vu l'escargot, Nina ? Oui, maman. Il va tout doux. Tout doux, oui. Comme la goutte. En ce moment, Nina tient l'arrosoir bleu. L'eau est tiède contre ses mains. Le bec verse un filet mince. J'arrose la menthe. Doucement. La menthe aime l'eau, pas trop. Chouchou arrive près des pots. Ses pieds sont un peu mouillés. Il regarde l'arrosoir bleu. Je peux, Nina ? Nina serre l'arrosoir un moment. Tu peux prêter, Nina. Prêter, c'est laisser Chouchou arroser. Puis tu attends ton tour. Tu peux. C'est ton tour. Nina tend l'arrosoir. Chouchou arrose le basilic. Ça sent le vert, encore plus. Nina s'assoit près de maman. Elle attend. Elle compte les gouttes du robinet. Une. Deux. Trois. Tu attends ton tour. Bravo, Nina. Chouchou rend l'arrosoir. C'est ton tour. Nina arrose la menthe encore un peu. Les feuilles brillent. Puis Chouchou le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Le seau ? Oui. Le seau est près des pots. Nina prend le seau rouge. Chouchou y met une petite pierre. Ils font un gâteau de terre. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. C'est du bon travail. Le gâteau de terre est rond ? Oui, maman. L'escargot a avancé d'une feuille.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Cécile est au jardin avec maman. Elle tient un petit arrosoir bleu. L'eau est tiède. Lila arrive. Lila aimerait l'arrosoir. Cécile peut prêter.
-enfant-f|Tu peux. C'est ton tour. Elle tend l'arrosoir.
-narrateur|Lila arrose le basilic. Ça sent le vert. Cécile attend son tour. Elle s'assoit près de maman.
-maman|On peut prêter. On peut attendre son tour. On peut aussi proposer un autre jeu.
-narrateur|Cécile prend un seau.
-narrateur|Un autre jeu, le seau.
-narrateur|Lila finit. Elle rend l'arrosoir. Cécile arrose la menthe. Parce qu'elle a su prêter, le jeu continue. Maman sourit.
-enfant-f|C'est ton tour, puis le mien.</t>
+          <t>narrateur|Le robinet du jardin goutte.
+narrateur|Tic.
+narrateur|Tic.
+narrateur|La terre des pots est encore sombre.
+narrateur|Ça sent la menthe.
+narrateur|Maman a un tablier mouillé.
+narrateur|Un escargot avance sur une feuille.
+maman|Tu as vu l'escargot, Nina ?
+enfant-f|Oui, maman.
+enfant-f|Il va tout doux.
+maman|Tout doux, oui.
+maman|Comme la goutte.
+narrateur|En ce moment, Nina tient l'arrosoir bleu.
+narrateur|L'eau est tiède contre ses mains.
+narrateur|Le bec verse un filet mince.
+enfant-f|J'arrose la menthe.
+maman|Doucement.
+maman|La menthe aime l'eau, pas trop.
+narrateur|Chouchou arrive près des pots.
+narrateur|Ses pieds sont un peu mouillés.
+narrateur|Il regarde l'arrosoir bleu.
+enfant-m|Je peux, Nina ?
+narrateur|Nina serre l'arrosoir un moment.
+maman|Tu peux prêter, Nina.
+maman|Prêter, c'est laisser Chouchou arroser.
+maman|Puis tu attends ton tour.
+enfant-f|Tu peux.
+enfant-f|C'est ton tour.
+narrateur|Nina tend l'arrosoir.
+narrateur|Chouchou arrose le basilic.
+narrateur|Ça sent le vert, encore plus.
+narrateur|Nina s'assoit près de maman.
+narrateur|Elle attend.
+narrateur|Elle compte les gouttes du robinet.
+enfant-f|Une.
+enfant-f|Deux.
+enfant-f|Trois.
+maman|Tu attends ton tour.
+maman|Bravo, Nina.
+narrateur|Chouchou rend l'arrosoir.
+enfant-m|C'est ton tour.
+narrateur|Nina arrose la menthe encore un peu.
+narrateur|Les feuilles brillent.
+narrateur|Puis Chouchou le voudrait encore.
+maman|Tu peux proposer un autre jeu.
+maman|Un autre jeu, c'est possible.
+enfant-f|Le seau ?
+maman|Oui.
+maman|Le seau est près des pots.
+narrateur|Nina prend le seau rouge.
+narrateur|Chouchou y met une petite pierre.
+narrateur|Ils font un gâteau de terre.
+maman|Vous avez prêté.
+maman|Chacun a eu son tour.
+maman|Puis un autre jeu.
+maman|C'est du bon travail.
+maman|Le gâteau de terre est rond ?
+enfant-f|Oui, maman.
+narrateur|L'escargot a avancé d'une feuille.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila veut l'arrosoir. Que peut faire Cécile ?</t>
+          <t>Chouchou veut l'arrosoir. Que peut faire Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila veut l'arrosoir. Que peut faire Cécile ?</t>
+          <t>narrateur|Chouchou veut l'arrosoir.
+narrateur|Que peut faire Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Cécile a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
+          <t>Nina a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté. Tu as attendu. Bravo, Nina. C'est du bon travail. Le seau est encore plein ? Un peu. Un autre jeu, c'est bien aussi. La menthe sent fort, tout près. Le robinet goutte encore, plus lent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1743,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Cécile a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
+          <t>narrateur|Nina a su prêter.
+narrateur|Elle a attendu son tour.
+narrateur|Elle a proposé un autre jeu.
+maman|Tu as prêté.
+maman|Tu as attendu.
+maman|Bravo, Nina.
+maman|C'est du bon travail.
+maman|Le seau est encore plein ?
+enfant-f|Un peu.
+maman|Un autre jeu, c'est bien aussi.
+narrateur|La menthe sent fort, tout près.
+narrateur|Le robinet goutte encore, plus lent.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Cécile et Lila rangent l'arrosoir. Maman ferme le robinet.</t>
+          <t>Nina et Chouchou rangent l'arrosoir. Maman ferme le robinet. Le seau aussi, près du mur ? Oui, maman. Le seau tape le mur, tout léger. Tes mains sont mouillées. On les sèche au tablier ? Oui. Le tablier est un peu rêche. Merci d'avoir prêté. Merci d'avoir attendu ton tour.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1918,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Cécile et Lila rangent l'arrosoir. Maman ferme le robinet.</t>
+          <t>narrateur|Nina et Chouchou rangent l'arrosoir.
+narrateur|Maman ferme le robinet.
+maman|Le seau aussi, près du mur ?
+enfant-f|Oui, maman.
+narrateur|Le seau tape le mur, tout léger.
+maman|Tes mains sont mouillées.
+maman|On les sèche au tablier ?
+enfant-f|Oui.
+narrateur|Le tablier est un peu rêche.
+maman|Merci d'avoir prêté.
+maman|Merci d'avoir attendu ton tour.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai prêté. Puis le seau. Bravo. Tu as fait du bon travail. L'escargot est arrivé au bord. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2096,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai prêté.
+enfant-f|Puis le seau.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'escargot est arrivé au bord.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le robinet du jardin goutte. Tic. Tic. La terre des pots est encore sombre. Ça sent la menthe. Maman a un tablier mouillé. Un escargot avance sur une feuille. Tu as vu l'escargot, Nina ? Oui, maman. Il va tout doux. Tout doux, oui. Comme la goutte. En ce moment, Nina tient l'arrosoir bleu. L'eau est tiède contre ses mains. Le bec verse un filet mince. J'arrose la menthe. Doucement. La menthe aime l'eau, pas trop. Chouchou arrive près des pots. Ses pieds sont un peu mouillés. Il regarde l'arrosoir bleu. Je peux, Nina ? Nina serre l'arrosoir un moment. Tu peux prêter, Nina. Prêter, c'est laisser Chouchou arroser. Puis tu attends ton tour. Tu peux. C'est ton tour. Nina tend l'arrosoir. Chouchou arrose le basilic. Ça sent le vert, encore plus. Nina s'assoit près de maman. Elle attend. Elle compte les gouttes du robinet. Une. Deux. Trois. Tu attends ton tour. Bravo, Nina. Chouchou rend l'arrosoir. C'est ton tour. Nina arrose la menthe encore un peu. Les feuilles brillent. Puis Chouchou le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Le seau ? Oui. Le seau est près des pots. Nina prend le seau rouge. Chouchou y met une petite pierre. Ils font un gâteau de terre. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. C'est du bon travail. Le gâteau de terre est rond ? Oui, maman. L'escargot a avancé d'une feuille.</t>
+          <t>Le robinet du jardin goutte. Tic. Tic. La terre des pots est encore sombre. Ça sent la menthe. Maman a un tablier mouillé. Un escargot avance sur une feuille. Tu as vu l'escargot, Nina ? Oui, maman. Il va tout doux. Tout doux, oui. Comme la goutte. En ce moment, Nina tient l'arrosoir bleu. L'eau est tiède contre ses mains. Le bec verse un filet mince. J'arrose la menthe. Doucement. La menthe aime l'eau, pas trop. Chouchou arrive près des pots. Ses pieds sont un peu mouillés. Il regarde l'arrosoir bleu. Je peux, Nina ? Nina serre l'arrosoir un moment. Tu peux prêter, Nina. Prêter, c'est laisser Chouchou arroser. Puis tu attends ton tour. Tu peux. C'est ton tour. Nina tend l'arrosoir. Chouchou arrose le basilic. Ça sent le vert, encore plus. Nina s'assoit près de maman. Elle attend. Elle compte les gouttes du robinet. Une. Deux. Trois. Tu attends ton tour. Bravo, Nina. Chouchou rend l'arrosoir. C'est ton tour. Nina arrose la menthe encore un peu. Les feuilles brillent. Puis Chouchou le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Le seau ? Oui. Le seau est près des pots. Nina prend le seau rouge. Chouchou y met une petite pierre. Ils font un gâteau de terre. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. Le gâteau de terre est rond ? Oui, maman. L'escargot a avancé d'une feuille.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cécile est au jardin avec maman. Elle tient un petit arrosoir bleu. L'eau est tiède. Lila arrive. Lila aimerait l'arrosoir. Cécile peut &lt;emphasis level="moderate"&gt;prêter&lt;/emphasis&gt;. Cécile dit : tu peux. C'est ton tour. Elle tend l'arrosoir. Lila arrose le basilic. Ça sent le vert. Cécile attend son tour. Elle s'assoit près de maman. Maman dit : on peut prêter. On peut attendre son tour. On peut aussi proposer un autre jeu. Cécile prend un seau. Elle dit : un autre jeu, le seau. Lila finit. Elle rend l'arrosoir. Cécile arrose la menthe. Parce qu'elle a su prêter, le jeu continue. Maman sourit. Cécile dit : c'est ton tour, puis le mien.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le robinet du jardin goutte. Tic. Tic. La terre des pots est encore sombre. Ça sent la menthe. Maman a un tablier mouillé. Un escargot avance sur une feuille. Tu as vu l'escargot, Nina ? Oui, maman. Il va tout doux. Tout doux, oui. Comme la goutte. En ce moment, Nina tient l'arrosoir bleu. L'eau est tiède contre ses mains. Le bec verse un filet mince. J'arrose la menthe. Doucement. La menthe aime l'eau, pas trop. Chouchou arrive près des pots. Ses pieds sont un peu mouillés. Il regarde l'arrosoir bleu. Je peux, Nina ? Nina serre l'arrosoir un moment. Tu peux prêter, Nina. Prêter, c'est laisser Chouchou arroser. Puis tu attends ton tour. Tu peux. C'est ton tour. Nina tend l'arrosoir. Chouchou arrose le basilic. Ça sent le vert, encore plus. Nina s'assoit près de maman. Elle attend. Elle compte les gouttes du robinet. Une. Deux. Trois. Tu attends ton tour. Bravo, Nina. Chouchou rend l'arrosoir. C'est ton tour. Nina arrose la menthe encore un peu. Les feuilles brillent. Puis Chouchou le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Le seau ? Oui. Le seau est près des pots. Nina prend le seau rouge. Chouchou y met une petite pierre. Ils font un gâteau de terre. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. Le gâteau de terre est rond ? Oui, maman. L'escargot a avancé d'une feuille.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,6 @@
 maman|Vous avez prêté.
 maman|Chacun a eu son tour.
 maman|Puis un autre jeu.
-maman|C'est du bon travail.
 maman|Le gâteau de terre est rond ?
 enfant-f|Oui, maman.
 narrateur|L'escargot a avancé d'une feuille.</t>
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila veut l'arrosoir. Que peut faire Cécile ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou veut l'arrosoir. Que peut faire Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1573,6 @@
 narrateur|Que peut faire Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1599,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté. Tu as attendu. Bravo, Nina. C'est du bon travail. Le seau est encore plein ? Un peu. Un autre jeu, c'est bien aussi. La menthe sent fort, tout près. Le robinet goutte encore, plus lent.</t>
+          <t>Nina a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté. Tu as attendu. Bravo, Nina. Le seau est encore plein ? Un peu. Un autre jeu, c'est bien aussi. La menthe sent fort, tout près. Le robinet goutte encore, plus lent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cécile a su &lt;emphasis level="moderate"&gt;prêter&lt;/emphasis&gt;. Elle a attendu son tour. Elle a proposé un autre jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a su prêter. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté. Tu as attendu. Bravo, Nina. Le seau est encore plein ? Un peu. Un autre jeu, c'est bien aussi. La menthe sent fort, tout près. Le robinet goutte encore, plus lent.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,7 +1747,6 @@
 maman|Tu as prêté.
 maman|Tu as attendu.
 maman|Bravo, Nina.
-maman|C'est du bon travail.
 maman|Le seau est encore plein ?
 enfant-f|Un peu.
 maman|Un autre jeu, c'est bien aussi.
@@ -1757,7 +1754,6 @@
 narrateur|Le robinet goutte encore, plus lent.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cécile et Lila rangent l'arrosoir. Maman ferme le robinet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina et Chouchou rangent l'arrosoir. Maman ferme le robinet. Le seau aussi, près du mur ? Oui, maman. Le seau tape le mur, tout léger. Tes mains sont mouillées. On les sèche au tablier ? Oui. Le tablier est un peu rêche. Merci d'avoir prêté. Merci d'avoir attendu ton tour.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,7 +1927,6 @@
 maman|Merci d'avoir attendu ton tour.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai prêté. Puis le seau. Bravo. Tu as fait du bon travail. L'escargot est arrivé au bord. L'histoire est finie.</t>
+          <t>J'ai prêté. Puis le seau. Bravo. L'escargot est arrivé au bord.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai prêté. Puis le seau. Bravo. L'escargot est arrivé au bord.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2094,9 @@
           <t>enfant-f|J'ai prêté.
 enfant-f|Puis le seau.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'escargot est arrivé au bord.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'escargot est arrivé au bord.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cécile, Lila, maman</t>
+          <t>Nina, Chouchou, maman</t>
         </is>
       </c>
     </row>
